--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,392 +656,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45872</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45781</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45690</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45592</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45501</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45410</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45319</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44409</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44318</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44136</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44045</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43954</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43863</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43772</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2145000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1910000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1581000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2062000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2093000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1911000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1698000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2038000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1964000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1741000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1440000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1827000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1861000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1574000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1374000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1818000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1861000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1598000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1246500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1404800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1297600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1055000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>831800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1012500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>955900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>842100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>733200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>952100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1572000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1153000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1501000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1533000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1401000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1247000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1495000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1446000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1273000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1056000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1333000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1360000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1135000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1001000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1318000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1360000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1177000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>919100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1034200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>972400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>798000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>627600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>768100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>725300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>642900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>552400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>726100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>520000</v>
+      </c>
+      <c r="F10" s="3">
         <v>428000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>561000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>560000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>510000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>451000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>543000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>518000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>468000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>384000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>494000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>501000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>439000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>373000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>500000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>501000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>421000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>327400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>370600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>325200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>257000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>204200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>244400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>230600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>199200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>180800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>226000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1072,8 +1098,10 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1158,8 +1186,14 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1244,8 +1278,14 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1285,36 +1325,36 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>50400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1324,100 +1364,112 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F15" s="3">
         <v>46000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>46000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>45000</v>
       </c>
       <c r="G15" s="3">
         <v>46000</v>
       </c>
       <c r="H15" s="3">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="I15" s="3">
         <v>46000</v>
       </c>
       <c r="J15" s="3">
+        <v>48000</v>
+      </c>
+      <c r="K15" s="3">
         <v>46000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="M15" s="3">
         <v>43000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>38000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>37000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>37000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>35000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>36000</v>
       </c>
       <c r="Q15" s="3">
         <v>35000</v>
       </c>
       <c r="R15" s="3">
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="S15" s="3">
         <v>35000</v>
       </c>
       <c r="T15" s="3">
+        <v>34000</v>
+      </c>
+      <c r="U15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="V15" s="3">
         <v>35400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>35200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>33600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>34000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>34600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>34900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>34300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>33500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>32800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>33100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1445,180 +1497,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1918000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1733000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1463000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1842000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1880000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1740000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1574000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1815000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1760000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1573000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1324000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1610000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1635000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1393000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1250000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1584000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1624000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1418000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1138200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1257600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1248200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>986000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>799200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>947800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>896400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>813400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>712000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>898500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>177000</v>
+      </c>
+      <c r="F18" s="3">
         <v>118000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>220000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>213000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>171000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>124000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>223000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>204000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>168000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>116000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>217000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>226000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>181000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>124000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>234000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>237000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>180000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>108300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>147200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>49400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>69000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>32600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>64700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>59500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>28700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>21200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>53600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1649,20 +1715,22 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1690,11 +1758,11 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1735,352 +1803,382 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>221000</v>
+      </c>
+      <c r="F21" s="3">
         <v>169000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>266000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>258000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>217000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>172000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>269000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>250000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>211000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>154000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>254000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>263000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>216000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>162000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>271000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>274000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>216000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>146000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>184300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>86900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>106700</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>65800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F22" s="3">
         <v>29000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>30000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>31000</v>
       </c>
       <c r="G22" s="3">
         <v>30000</v>
       </c>
       <c r="H22" s="3">
-        <v>36000</v>
+        <v>31000</v>
       </c>
       <c r="I22" s="3">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="J22" s="3">
         <v>36000</v>
       </c>
       <c r="K22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="M22" s="3">
         <v>34000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>22000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>20000</v>
       </c>
       <c r="N22" s="3">
         <v>22000</v>
       </c>
       <c r="O22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>17000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>20000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>16000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>17000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>13000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>12700</v>
       </c>
       <c r="U22" s="3">
         <v>13000</v>
       </c>
       <c r="V22" s="3">
+        <v>12700</v>
+      </c>
+      <c r="W22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="X22" s="3">
         <v>36800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>36000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>35300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>35600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>35000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>33200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>33100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>29200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F23" s="3">
         <v>94000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>190000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>182000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>141000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>88000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>187000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>168000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>134000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>94000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>197000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>204000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>164000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>104000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>218000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>220000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>167000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>95600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>134200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>12600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>33000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>29100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>24500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>24400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F24" s="3">
         <v>21000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>47000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>41000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>36000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>21000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>47000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>42000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>33000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>18000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>39000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>40000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>31000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>20000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>40000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>38000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>30000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>16800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>24900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>6000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>300</v>
       </c>
       <c r="AB24" s="3">
         <v>400</v>
       </c>
       <c r="AC24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2165,180 +2263,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>113000</v>
+      </c>
+      <c r="F26" s="3">
         <v>73000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>143000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>141000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>105000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>67000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>140000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>126000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>101000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>76000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>158000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>164000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>133000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>84000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>178000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>182000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>137000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>78800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>109300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>9500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>27000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>26200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>24100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>24600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>108000</v>
+      </c>
+      <c r="F27" s="3">
         <v>70000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>137000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>134000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>100000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>64000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>133000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>119000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>95000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>63000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>112000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>110000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>86000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>54000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>111000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>115000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>86000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>47700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>64400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>26500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>27000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>26200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>24100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>24600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2423,8 +2539,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2509,8 +2631,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2595,8 +2723,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2681,20 +2815,26 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2722,11 +2862,11 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2767,94 +2907,106 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>108000</v>
+      </c>
+      <c r="F33" s="3">
         <v>70000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>137000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>134000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>100000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>64000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>133000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>119000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>95000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>63000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>112000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>110000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>86000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>54000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>111000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>115000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>86000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>47700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>64400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>26500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>27000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>26200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>24100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>24600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2939,185 +3091,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>108000</v>
+      </c>
+      <c r="F35" s="3">
         <v>70000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>137000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>134000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>100000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>64000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>133000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>119000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>95000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>63000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>112000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>110000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>86000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>54000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>111000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>115000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>86000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>47700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>64400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>26500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>27000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>26200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>24100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>24600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45872</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45781</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45690</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45592</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45501</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45410</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45319</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44409</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44318</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44136</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44045</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43954</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43863</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43772</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3148,8 +3318,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3180,77 +3352,79 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F41" s="3">
         <v>220000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>89000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>25000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>13000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>30000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>101000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>20000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>177000</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>1000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>66600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>320200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3266,26 +3440,32 @@
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F42" s="3">
         <v>10000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>16000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>22000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3352,77 +3532,83 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1439000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1048000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1342000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1357000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1319000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1066000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1378000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1294000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1200000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>973000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1215000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1231000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1098000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>955000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1273000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1264000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1113000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>884000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>946100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>832900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>716100</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3438,77 +3624,83 @@
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1137000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1103000</v>
+      </c>
+      <c r="F44" s="3">
         <v>986000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1016000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1056000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1069000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>908000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>950000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>959000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>945000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>766000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>824000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>896000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1030000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1047000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1148000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1166000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1063000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>856000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>721200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>593200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>509200</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3524,8 +3716,14 @@
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3565,36 +3763,36 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>32000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>34000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>31000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>25000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>26000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>24700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>15600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>17300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3610,77 +3808,83 @@
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2937000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2557000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2302000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2507000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2510000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2444000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2025000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2381000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2318000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2223000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1773000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2171000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2182000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2166000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2211000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2455000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2461000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2202000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1767000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1696900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1508300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1562800</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3696,53 +3900,59 @@
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>6000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>28000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>40000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>44000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>54000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>91000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>66000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>82000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>85000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>76000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -3782,77 +3992,83 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>481000</v>
+      </c>
+      <c r="F48" s="3">
         <v>465000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>455000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>450000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>439000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>412000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>387000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>369000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>366000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>343000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>326000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>314000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>299000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>280000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>268000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>267000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>252000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>246000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>249400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>226400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>227400</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3868,77 +4084,83 @@
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2712000</v>
+      </c>
+      <c r="F49" s="3">
         <v>2743000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2765000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2765000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2800000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2833000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2848000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2797000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2816000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2345000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2334000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>2363000</v>
       </c>
       <c r="O49" s="3">
         <v>2334000</v>
       </c>
       <c r="P49" s="3">
+        <v>2363000</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>2334000</v>
+      </c>
+      <c r="R49" s="3">
         <v>2330000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2359000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2351000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2361000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2386000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2414700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2314200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2013000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3954,8 +4176,14 @@
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4040,8 +4268,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4126,74 +4360,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F52" s="3">
         <v>4000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1000</v>
       </c>
       <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
+      <c r="I52" s="3">
+        <v>1000</v>
       </c>
       <c r="J52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3">
         <v>3000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>5000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>88000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>108000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>69000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>79000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>35000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>19800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>4400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4206,14 +4446,20 @@
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4298,77 +4544,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6709000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6324000</v>
+      </c>
+      <c r="F54" s="3">
         <v>6085000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6300000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6306000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6278000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5870000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6215000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6098000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6041000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5069000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5067000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5039000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4929000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>4909000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5190000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5148000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>4894000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4434000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4380800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>4053300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3803200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4384,8 +4636,14 @@
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4416,8 +4674,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4448,77 +4708,79 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>815000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>814000</v>
+      </c>
+      <c r="F57" s="3">
         <v>512000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>734000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>758000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>923000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>562000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>782000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>738000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>777000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>504000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>646000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>601000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>581000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>479000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>701000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>826000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>859000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>608000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>613300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>564900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>532500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4534,52 +4796,58 @@
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>108000</v>
+      </c>
+      <c r="F58" s="3">
         <v>119000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>120000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>120000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>111000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>91000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>95000</v>
       </c>
       <c r="J58" s="3">
         <v>91000</v>
       </c>
       <c r="K58" s="3">
+        <v>95000</v>
+      </c>
+      <c r="L58" s="3">
+        <v>91000</v>
+      </c>
+      <c r="M58" s="3">
         <v>84000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>70000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>69000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>71000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>70000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>15000</v>
       </c>
       <c r="R58" s="3">
         <v>15000</v>
@@ -4597,14 +4865,14 @@
         <v>15000</v>
       </c>
       <c r="W58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="X58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>13000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4620,77 +4888,83 @@
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>119000</v>
+      </c>
+      <c r="F59" s="3">
         <v>120000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>146000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>145000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>144000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>90000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>125000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>103000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>109000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>94000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>106000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>96000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>87000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>232000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>271000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>238000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>192000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>216000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>214300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>164900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>148600</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4706,77 +4980,83 @@
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="F60" s="3">
         <v>874000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1107000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1117000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1246000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>866000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1114000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1012000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1038000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>774000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>921000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>842000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>798000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>726000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>987000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1079000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1066000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>839000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>842600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>744800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>694100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4792,77 +5072,83 @@
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2653000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2343000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2338000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2336000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2437000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2435000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2415000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2542000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2550000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2546000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2001000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1566000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1683000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1694000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1444000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1537000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1592000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1510000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1456000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1459000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1462000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2251500</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4878,77 +5164,83 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>672000</v>
+      </c>
+      <c r="F62" s="3">
         <v>710000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>713000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>702000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>689000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>728000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>724000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>732000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>721000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>722000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>317000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>253000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>205000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>329000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>314000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>312000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>312000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>308000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>320500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>298500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>158500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4964,8 +5256,14 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5050,8 +5348,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5136,8 +5440,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5222,77 +5532,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4605000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4210000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4011000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4245000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4344000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4457000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4096000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4465000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4378000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4397000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3545000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2852000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2826000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2737000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3162000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3486000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3598000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3458000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3109000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3157500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2981400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3104100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5308,8 +5624,14 @@
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5340,8 +5662,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5426,8 +5750,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5512,8 +5842,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5598,8 +5934,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5684,74 +6026,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>786000</v>
+      </c>
+      <c r="F72" s="3">
         <v>755000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>736000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>642000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>515000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>449000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>433000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>385000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>284000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>189000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>491000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>447000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>403000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>458000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>404000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>298000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>180000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>92000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>44400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-20000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5764,14 +6112,20 @@
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5856,8 +6210,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5942,8 +6302,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6028,77 +6394,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2031000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="F76" s="3">
         <v>1997000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1977000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1886000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1744000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1698000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1671000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1644000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1570000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1451000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1769000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1695000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1628000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1747000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1704000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1550000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1436000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1325000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1223300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1071900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>699100</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6114,8 +6486,14 @@
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6200,185 +6578,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45872</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45781</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45690</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45592</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45501</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45410</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45319</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44409</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44318</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44136</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44045</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43954</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43863</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43772</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>108000</v>
+      </c>
+      <c r="F81" s="3">
         <v>70000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>137000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>134000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>100000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>64000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>133000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>119000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>95000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>63000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>112000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>110000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>86000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>54000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>111000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>115000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>86000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>47700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>64400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>26500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>27000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>26200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>24100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>24600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6409,8 +6805,10 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6418,22 +6816,22 @@
         <v>11000</v>
       </c>
       <c r="E83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="F83" s="3">
         <v>11000</v>
       </c>
       <c r="G83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H83" s="3">
         <v>11000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J83" s="3">
         <v>9000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7000</v>
       </c>
       <c r="K83" s="3">
         <v>8000</v>
@@ -6442,44 +6840,44 @@
         <v>7000</v>
       </c>
       <c r="M83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N83" s="3">
         <v>7000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P83" s="3">
         <v>8000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>6000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>38000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>37000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>37000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>36000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>37700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>37100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>37500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>37700</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6495,8 +6893,14 @@
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6581,8 +6985,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6667,8 +7077,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6753,8 +7169,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6839,8 +7261,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6925,77 +7353,83 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>82000</v>
+      </c>
+      <c r="F89" s="3">
         <v>268000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>271000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>34000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>77000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>235000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>260000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>48000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>78000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>294000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>373000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>282000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>120000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>307000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>154000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-23000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-37000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>35200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>32900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-56600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-42500</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7011,8 +7445,14 @@
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7043,77 +7483,79 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-15000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-8000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-10000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-13000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-11000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-8000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-9000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-7000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-19000</v>
       </c>
       <c r="N91" s="3">
         <v>-5000</v>
       </c>
       <c r="O91" s="3">
-        <v>-10000</v>
+        <v>-19000</v>
       </c>
       <c r="P91" s="3">
         <v>-5000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-5000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-9000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-6000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-8000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-3900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-4100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
@@ -7129,8 +7571,14 @@
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7215,8 +7663,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7301,77 +7755,83 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-74000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-43000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-16000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-31000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-139000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-44000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-574000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-88000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-18000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-90000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-74000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-77000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-45000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-11000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-14100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-176000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-9000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-3900</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7387,8 +7847,14 @@
       <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7419,8 +7885,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7460,11 +7928,11 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7505,8 +7973,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7591,8 +8065,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7677,8 +8157,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7763,77 +8249,83 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-63000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-164000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-61000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-206000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-124000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-21000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>525000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-306000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-274000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-173000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-222000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-111000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-77000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>67000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>48000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-25100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>81400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-188000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-14300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7849,8 +8341,14 @@
       <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7890,11 +8388,11 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7935,77 +8433,83 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="F102" s="3">
         <v>131000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>64000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>17000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-17000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>29000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>81000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>19000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-176000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>177000</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-4000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-61700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-253600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-60700</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
@@ -8019,6 +8523,12 @@
         <v>8</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
